--- a/data/contractors/derived-4700134228/sources/personnel_plan.xlsx
+++ b/data/contractors/derived-4700134228/sources/personnel_plan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Персонал" sheetId="1" r:id="R0336e1bd389d47da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План по месяцам" sheetId="2" r:id="R18b55e2f17564525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Персонал" sheetId="1" r:id="R5d09bd6de67340c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План по месяцам" sheetId="2" r:id="R3a702395896d4aeb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -340,10 +340,10 @@
         <x:v>Персонал</x:v>
       </x:c>
       <x:c r="K4" s="6" t="str">
-        <x:v>ИТОГО</x:v>
+        <x:v>План</x:v>
       </x:c>
       <x:c r="L4" s="6" t="str">
-        <x:v>Всего дней/машин</x:v>
+        <x:v>Всего дней</x:v>
       </x:c>
       <x:c r="M4" s="11" t="n">
         <x:v>45992.5</x:v>
